--- a/artfynd/A 32200-2023 artfynd.xlsx
+++ b/artfynd/A 32200-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32200-2023 artfynd.xlsx
+++ b/artfynd/A 32200-2023 artfynd.xlsx
@@ -3310,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG24" t="b">
         <v>0</v>

--- a/artfynd/A 32200-2023 artfynd.xlsx
+++ b/artfynd/A 32200-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104622371</v>
+        <v>104680936</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591172.0444014111</v>
+        <v>591097</v>
       </c>
       <c r="R2" t="n">
-        <v>7043130.940049943</v>
+        <v>7043173</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,33 +757,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104622444</v>
+        <v>104622317</v>
       </c>
       <c r="B3" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,12 +796,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591161.9291367272</v>
+        <v>591191</v>
       </c>
       <c r="R3" t="n">
-        <v>7043140.479575073</v>
+        <v>7043123</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -904,12 +887,7 @@
         <v>104622361</v>
       </c>
       <c r="B4" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,12 +904,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591172.0444014111</v>
+        <v>591172</v>
       </c>
       <c r="R4" t="n">
-        <v>7043130.940049943</v>
+        <v>7043130</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1014,15 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104622322</v>
+        <v>104622444</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,21 +1003,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591191.0615803688</v>
+        <v>591162</v>
       </c>
       <c r="R5" t="n">
-        <v>7043122.99569699</v>
+        <v>7043141</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1127,15 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104622193</v>
+        <v>104680955</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,35 +1111,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591125.3000591549</v>
+        <v>591170</v>
       </c>
       <c r="R6" t="n">
-        <v>7043107.263580035</v>
+        <v>7043203</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,22 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,33 +1182,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104622317</v>
+        <v>104680980</v>
       </c>
       <c r="B7" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,26 +1221,28 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591191.0615803688</v>
+        <v>591184</v>
       </c>
       <c r="R7" t="n">
-        <v>7043122.99569699</v>
+        <v>7043182</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1311,22 +1269,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,33 +1283,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104622265</v>
+        <v>104680988</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,35 +1313,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591171.1763499564</v>
+        <v>591204</v>
       </c>
       <c r="R8" t="n">
-        <v>7043098.747216359</v>
+        <v>7043191</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1424,22 +1370,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>08:45</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,72 +1384,65 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104680987</v>
+        <v>107173380</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591204.3169762525</v>
+        <v>591161</v>
       </c>
       <c r="R9" t="n">
-        <v>7043191.284554873</v>
+        <v>7043198</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1540,22 +1469,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2023-03-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2023-03-07</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,34 +1493,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104680980</v>
+        <v>107173482</v>
       </c>
       <c r="B10" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,28 +1531,26 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591184.4575665609</v>
+        <v>591195</v>
       </c>
       <c r="R10" t="n">
-        <v>7043181.780604665</v>
+        <v>7043190</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,22 +1577,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2023-03-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2023-03-07</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,34 +1601,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104680958</v>
+        <v>104622265</v>
       </c>
       <c r="B11" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,19 +1648,17 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Getstugeberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591169.9872038455</v>
+        <v>591171</v>
       </c>
       <c r="R11" t="n">
-        <v>7043202.811189404</v>
+        <v>7043099</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1772,22 +1685,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,77 +1709,64 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104680967</v>
+        <v>104622322</v>
       </c>
       <c r="B12" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Getstugeberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591156.9859250421</v>
+        <v>591191</v>
       </c>
       <c r="R12" t="n">
-        <v>7043203.779369339</v>
+        <v>7043123</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1893,22 +1793,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,77 +1817,64 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104680972</v>
+        <v>104622371</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Getstugeberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591154.9424237387</v>
+        <v>591172</v>
       </c>
       <c r="R13" t="n">
-        <v>7043212.656174552</v>
+        <v>7043130</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2014,22 +1901,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,34 +1925,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104680955</v>
+        <v>104622518</v>
       </c>
       <c r="B14" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,37 +1954,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Getstugeberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591169.9872038455</v>
+        <v>591226</v>
       </c>
       <c r="R14" t="n">
-        <v>7043202.811189404</v>
+        <v>7043215</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2130,22 +2009,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,66 +2033,55 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104680978</v>
+        <v>104680958</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2221,10 +2089,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>591184.4575665609</v>
+        <v>591170</v>
       </c>
       <c r="R15" t="n">
-        <v>7043181.780604665</v>
+        <v>7043203</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2254,19 +2122,9 @@
           <t>2022-11-15</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,47 +2152,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104680984</v>
+        <v>104681041</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2342,10 +2190,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>591193.9720722865</v>
+        <v>591212</v>
       </c>
       <c r="R16" t="n">
-        <v>7043193.222189298</v>
+        <v>7043205</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2375,19 +2223,9 @@
           <t>2022-11-15</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2415,15 +2253,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104680988</v>
+        <v>107173397</v>
       </c>
       <c r="B17" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2431,37 +2264,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>591204.3169762525</v>
+        <v>591164</v>
       </c>
       <c r="R17" t="n">
-        <v>7043191.284554873</v>
+        <v>7043197</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2488,22 +2319,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2023-03-07</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
+          <t>2023-03-07</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,62 +2343,55 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104680948</v>
+        <v>104682105</v>
       </c>
       <c r="B18" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1503</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2575,10 +2399,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591148.1738116825</v>
+        <v>591095</v>
       </c>
       <c r="R18" t="n">
-        <v>7043183.422695331</v>
+        <v>7043181</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2608,27 +2432,18 @@
           <t>2022-11-15</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-11-15</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2647,15 +2462,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>107173482</v>
+        <v>104680940</v>
       </c>
       <c r="B19" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,35 +2473,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>591195.4025387656</v>
+        <v>591097</v>
       </c>
       <c r="R19" t="n">
-        <v>7043190.135775584</v>
+        <v>7043173</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2718,22 +2530,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-03-07</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:05</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-03-07</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:05</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2742,55 +2544,51 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>107173345</v>
+        <v>107173505</v>
       </c>
       <c r="B20" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2801,10 +2599,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>591154.2274208536</v>
+        <v>591183</v>
       </c>
       <c r="R20" t="n">
-        <v>7043190.744211345</v>
+        <v>7043190</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2836,7 +2634,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2846,7 +2644,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2873,51 +2671,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>107173505</v>
+        <v>104681108</v>
       </c>
       <c r="B21" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6055</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>591183.3335350434</v>
+        <v>591258</v>
       </c>
       <c r="R21" t="n">
-        <v>7043189.790246807</v>
+        <v>7043099</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2944,22 +2739,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-03-07</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:05</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-03-07</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:05</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2968,69 +2753,65 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>107173390</v>
+        <v>104622193</v>
       </c>
       <c r="B22" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Getstugeberget, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>591161.1877762482</v>
+        <v>591126</v>
       </c>
       <c r="R22" t="n">
-        <v>7043197.644909526</v>
+        <v>7043107</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3057,22 +2838,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-03-07</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-03-07</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3087,49 +2868,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>107173397</v>
+        <v>107173345</v>
       </c>
       <c r="B23" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3140,10 +2916,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>591164.3167694361</v>
+        <v>591155</v>
       </c>
       <c r="R23" t="n">
-        <v>7043197.734464967</v>
+        <v>7043190</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3175,7 +2951,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3185,7 +2961,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3212,15 +2988,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>107173686</v>
+        <v>104680874</v>
       </c>
       <c r="B24" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3228,40 +2999,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>591164.0367510475</v>
+        <v>591141</v>
       </c>
       <c r="R24" t="n">
-        <v>7043113.733347217</v>
+        <v>7043072</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3288,74 +3056,60 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-03-07</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-03-07</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>107173567</v>
+        <v>104680948</v>
       </c>
       <c r="B25" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3365,21 +3119,19 @@
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Getstugeberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>591206.3989755153</v>
+        <v>591148</v>
       </c>
       <c r="R25" t="n">
-        <v>7043181.068508918</v>
+        <v>7043183</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3406,22 +3158,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-03-07</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:11</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-03-07</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:11</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3436,15 +3178,873 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>107173567</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Getstugeberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>591206</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7043182</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-03-07</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-03-07</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
           <t>Daniel Rutschman</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
+      <c r="AX26" t="inlineStr">
         <is>
           <t>Daniel Rutschman</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>107173686</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Getstugeberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>591164</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7043114</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-03-07</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-03-07</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>104680972</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Getstugeberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>591155</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7043213</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>104680978</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Getstugeberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>591184</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7043182</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>104680984</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Getstugeberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>591194</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7043193</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>104680987</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Getstugeberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>591204</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7043191</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>104681033</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Getstugeberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>591212</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7043205</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>104680967</v>
+      </c>
+      <c r="B33" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Getstugeberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>591157</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7043204</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32200-2023 artfynd.xlsx
+++ b/artfynd/A 32200-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104680936</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104622317</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104622361</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104622444</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104680955</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104680980</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1400,6 +1435,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104680988</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107173380</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,6 +1661,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107173482</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1724,6 +1774,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104622265</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1832,6 +1887,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104622322</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1940,6 +2000,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104622371</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2048,6 +2113,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104622518</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2149,6 +2219,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104680958</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2250,6 +2325,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104681041</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2358,6 +2438,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107173397</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2459,6 +2544,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104682105</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2560,6 +2650,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104680940</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2668,6 +2763,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107173505</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2769,6 +2869,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104681108</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2877,6 +2982,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104622193</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2985,6 +3095,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107173345</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3086,6 +3201,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104680874</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3187,6 +3307,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104680948</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3300,6 +3425,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107173567</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3413,6 +3543,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107173686</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3519,6 +3654,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104680972</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3625,6 +3765,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104680978</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3731,6 +3876,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104680984</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3833,6 +3983,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104680987</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3939,6 +4094,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104681033</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4045,8 +4205,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104680967</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>